--- a/OUTPUT/reverse_A4FQD5_Saccharopolyspora_erythraea_NRRL_2338.xlsx
+++ b/OUTPUT/reverse_A4FQD5_Saccharopolyspora_erythraea_NRRL_2338.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.8742</v>
+        <v>0.8740503798480608</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.8818</v>
+        <v>0.8816473410635746</v>
       </c>
     </row>
   </sheetData>
